--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -3735,11 +3735,15 @@
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M56" s="3" t="n"/>
       <c r="N56" s="2" t="n"/>
     </row>
@@ -8145,11 +8149,15 @@
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M142" s="3" t="n"/>
       <c r="N142" s="2" t="n"/>
     </row>
@@ -12477,18 +12485,18 @@
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>类型分行齐全(烟感/温感/手报/消火栓/声光/显示盘/模块/其他+总计)</t>
+          <t>当有屏蔽设备时，其他类型显示了一个超级大的数字</t>
         </is>
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K224" s="2" t="n"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M224" s="3" t="n"/>
@@ -12725,18 +12733,19 @@
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>照片中屏蔽列空白,未见数值</t>
+          <t>照片中屏蔽列空白,未见数值。
+当有屏蔽时，每一行的屏蔽数据不能全部是 0</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M228" s="3" t="n"/>
@@ -12970,11 +12979,15 @@
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K232" s="2" t="n"/>
-      <c r="L232" s="2" t="n"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M232" s="3" t="n"/>
       <c r="N232" s="2" t="n"/>
     </row>
@@ -13070,11 +13083,15 @@
       <c r="I234" s="3" t="n"/>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K234" s="2" t="n"/>
-      <c r="L234" s="2" t="n"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M234" s="3" t="n"/>
       <c r="N234" s="2" t="n"/>
     </row>
@@ -13120,11 +13137,15 @@
       <c r="I235" s="3" t="n"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K235" s="2" t="n"/>
-      <c r="L235" s="2" t="n"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M235" s="3" t="n"/>
       <c r="N235" s="2" t="n"/>
     </row>
@@ -13170,11 +13191,15 @@
       <c r="I236" s="3" t="n"/>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K236" s="2" t="n"/>
-      <c r="L236" s="2" t="n"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M236" s="3" t="n"/>
       <c r="N236" s="2" t="n"/>
     </row>
@@ -13220,11 +13245,15 @@
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K237" s="2" t="n"/>
-      <c r="L237" s="2" t="n"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M237" s="3" t="n"/>
       <c r="N237" s="2" t="n"/>
     </row>
@@ -13274,13 +13303,13 @@
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K238" s="2" t="n"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M238" s="3" t="n"/>
@@ -13332,13 +13361,13 @@
       </c>
       <c r="J239" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M239" s="3" t="n"/>
@@ -13390,13 +13419,13 @@
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K240" s="2" t="n"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M240" s="3" t="n"/>
@@ -13444,13 +13473,13 @@
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K241" s="2" t="n"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M241" s="3" t="n"/>
@@ -13502,13 +13531,13 @@
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M242" s="3" t="n"/>
@@ -13560,13 +13589,13 @@
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K243" s="2" t="n"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M243" s="3" t="n"/>
@@ -13614,13 +13643,13 @@
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K244" s="2" t="n"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M244" s="3" t="n"/>
@@ -13672,13 +13701,13 @@
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K245" s="2" t="n"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M245" s="3" t="n"/>
@@ -13730,13 +13759,13 @@
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K246" s="2" t="n"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M246" s="3" t="n"/>
@@ -13780,11 +13809,15 @@
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K247" s="2" t="n"/>
-      <c r="L247" s="2" t="n"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M247" s="3" t="n"/>
       <c r="N247" s="2" t="n"/>
     </row>
@@ -13830,11 +13863,15 @@
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K248" s="2" t="n"/>
-      <c r="L248" s="2" t="n"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M248" s="3" t="n"/>
       <c r="N248" s="2" t="n"/>
     </row>
@@ -13884,13 +13921,13 @@
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K249" s="2" t="n"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M249" s="3" t="n"/>
@@ -13942,13 +13979,13 @@
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K250" s="2" t="n"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M250" s="3" t="n"/>
@@ -13996,11 +14033,15 @@
       <c r="I251" s="3" t="n"/>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K251" s="2" t="n"/>
-      <c r="L251" s="2" t="n"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M251" s="3" t="n"/>
       <c r="N251" s="2" t="n"/>
     </row>
@@ -17244,7 +17285,7 @@
       <c r="I313" s="3" t="n"/>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K313" s="2" t="n"/>
@@ -17291,14 +17332,22 @@
           <t>复位、手动启动、屏蔽、手自动转换等全部拒绝</t>
         </is>
       </c>
-      <c r="I314" s="3" t="n"/>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>一级操作员可以操作手自动切换/</t>
+        </is>
+      </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K314" s="2" t="n"/>
-      <c r="L314" s="2" t="n"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M314" s="3" t="n"/>
       <c r="N314" s="2" t="n"/>
     </row>
@@ -17344,7 +17393,11 @@
         </is>
       </c>
       <c r="K315" s="2" t="n"/>
-      <c r="L315" s="2" t="n"/>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M315" s="3" t="n"/>
       <c r="N315" s="2" t="n"/>
     </row>
@@ -17390,11 +17443,15 @@
       <c r="I316" s="3" t="n"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K316" s="2" t="n"/>
-      <c r="L316" s="2" t="n"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M316" s="3" t="n"/>
       <c r="N316" s="2" t="n"/>
     </row>
@@ -17444,7 +17501,11 @@
         </is>
       </c>
       <c r="K317" s="2" t="n"/>
-      <c r="L317" s="2" t="n"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M317" s="3" t="n"/>
       <c r="N317" s="2" t="n"/>
     </row>
@@ -18729,14 +18790,22 @@
           <t>见子项</t>
         </is>
       </c>
-      <c r="I341" s="3" t="n"/>
+      <c r="I341" s="3" t="inlineStr">
+        <is>
+          <t>节点监控，查询无响应</t>
+        </is>
+      </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K341" s="2" t="n"/>
-      <c r="L341" s="2" t="n"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M341" s="3" t="n"/>
       <c r="N341" s="2" t="inlineStr">
         <is>
@@ -19378,11 +19447,15 @@
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K352" s="2" t="n"/>
-      <c r="L352" s="2" t="n"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M352" s="3" t="n"/>
       <c r="N352" s="2" t="inlineStr">
         <is>
@@ -19432,11 +19505,15 @@
       <c r="I353" s="3" t="n"/>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K353" s="2" t="n"/>
-      <c r="L353" s="2" t="n"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
           <t>⚠️机内监控"通信帧数"页不含电压/电量，本判据需另找电压显示页</t>
@@ -20978,11 +21055,15 @@
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K378" s="2" t="n"/>
-      <c r="L378" s="2" t="n"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M378" s="3" t="n"/>
       <c r="N378" s="2" t="inlineStr">
         <is>
@@ -21032,11 +21113,15 @@
       <c r="I379" s="3" t="n"/>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K379" s="2" t="n"/>
-      <c r="L379" s="2" t="n"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M379" s="3" t="n"/>
       <c r="N379" s="2" t="inlineStr">
         <is>
@@ -21338,7 +21423,7 @@
       </c>
       <c r="J384" s="8" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K384" s="2" t="n"/>
@@ -21884,7 +21969,7 @@
       </c>
       <c r="J393" s="8" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K393" s="2" t="n"/>
@@ -22863,14 +22948,23 @@
           <t>见子项</t>
         </is>
       </c>
-      <c r="I410" s="3" t="n"/>
+      <c r="I410" s="3" t="inlineStr">
+        <is>
+          <t>启动倒计时开始，声光报警器没有声音。
+倒计时结束后，声光报警器也没有声音。应该有喷洒声。</t>
+        </is>
+      </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K410" s="2" t="n"/>
-      <c r="L410" s="2" t="n"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M410" s="3" t="n"/>
       <c r="N410" s="2" t="n"/>
     </row>
@@ -24550,11 +24644,15 @@
       <c r="I444" s="3" t="n"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K444" s="2" t="n"/>
-      <c r="L444" s="2" t="n"/>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M444" s="3" t="n"/>
       <c r="N444" s="2" t="n"/>
     </row>
@@ -24600,11 +24698,15 @@
       <c r="I445" s="3" t="n"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K445" s="2" t="n"/>
-      <c r="L445" s="2" t="n"/>
+      <c r="L445" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M445" s="3" t="n"/>
       <c r="N445" s="2" t="n"/>
     </row>
@@ -26388,11 +26490,15 @@
       <c r="I481" s="3" t="n"/>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K481" s="2" t="n"/>
-      <c r="L481" s="2" t="n"/>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M481" s="3" t="n"/>
       <c r="N481" s="2" t="n"/>
     </row>
@@ -26438,11 +26544,15 @@
       <c r="I482" s="3" t="n"/>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K482" s="2" t="n"/>
-      <c r="L482" s="2" t="n"/>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M482" s="3" t="n"/>
       <c r="N482" s="2" t="n"/>
     </row>
@@ -26488,11 +26598,15 @@
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K483" s="2" t="n"/>
-      <c r="L483" s="2" t="n"/>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M483" s="3" t="n"/>
       <c r="N483" s="2" t="n"/>
     </row>
@@ -26538,11 +26652,15 @@
       <c r="I484" s="3" t="n"/>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K484" s="2" t="n"/>
-      <c r="L484" s="2" t="n"/>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M484" s="3" t="n"/>
       <c r="N484" s="2" t="n"/>
     </row>
@@ -26588,11 +26706,15 @@
       <c r="I485" s="3" t="n"/>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K485" s="2" t="n"/>
-      <c r="L485" s="2" t="n"/>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M485" s="3" t="n"/>
       <c r="N485" s="2" t="n"/>
     </row>
@@ -26634,11 +26756,15 @@
       <c r="I486" s="3" t="n"/>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K486" s="2" t="n"/>
-      <c r="L486" s="2" t="n"/>
+      <c r="L486" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M486" s="3" t="n"/>
       <c r="N486" s="2" t="n"/>
     </row>
@@ -26684,11 +26810,15 @@
       <c r="I487" s="3" t="n"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K487" s="2" t="n"/>
-      <c r="L487" s="2" t="n"/>
+      <c r="L487" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M487" s="3" t="n"/>
       <c r="N487" s="2" t="n"/>
     </row>
@@ -26734,11 +26864,15 @@
       <c r="I488" s="3" t="n"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K488" s="2" t="n"/>
-      <c r="L488" s="2" t="n"/>
+      <c r="L488" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M488" s="3" t="n"/>
       <c r="N488" s="2" t="n"/>
     </row>
@@ -26784,11 +26918,15 @@
       <c r="I489" s="3" t="n"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K489" s="2" t="n"/>
-      <c r="L489" s="2" t="n"/>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M489" s="3" t="n"/>
       <c r="N489" s="2" t="n"/>
     </row>
@@ -26834,11 +26972,15 @@
       <c r="I490" s="3" t="n"/>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K490" s="2" t="n"/>
-      <c r="L490" s="2" t="n"/>
+      <c r="L490" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M490" s="3" t="n"/>
       <c r="N490" s="2" t="n"/>
     </row>
@@ -26880,11 +27022,15 @@
       <c r="I491" s="3" t="n"/>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K491" s="2" t="n"/>
-      <c r="L491" s="2" t="n"/>
+      <c r="L491" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M491" s="3" t="n"/>
       <c r="N491" s="2" t="n"/>
     </row>
@@ -26930,11 +27076,15 @@
       <c r="I492" s="3" t="n"/>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K492" s="2" t="n"/>
-      <c r="L492" s="2" t="n"/>
+      <c r="L492" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M492" s="3" t="n"/>
       <c r="N492" s="2" t="n"/>
     </row>
@@ -26980,11 +27130,15 @@
       <c r="I493" s="3" t="n"/>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K493" s="2" t="n"/>
-      <c r="L493" s="2" t="n"/>
+      <c r="L493" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M493" s="3" t="n"/>
       <c r="N493" s="2" t="n"/>
     </row>
@@ -27026,11 +27180,15 @@
       <c r="I494" s="3" t="n"/>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K494" s="2" t="n"/>
-      <c r="L494" s="2" t="n"/>
+      <c r="L494" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M494" s="3" t="n"/>
       <c r="N494" s="2" t="n"/>
     </row>
@@ -27176,11 +27334,15 @@
       <c r="I497" s="3" t="n"/>
       <c r="J497" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K497" s="2" t="n"/>
-      <c r="L497" s="2" t="n"/>
+      <c r="L497" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M497" s="3" t="n"/>
       <c r="N497" s="2" t="n"/>
     </row>
@@ -27226,11 +27388,15 @@
       <c r="I498" s="3" t="n"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K498" s="2" t="n"/>
-      <c r="L498" s="2" t="n"/>
+      <c r="L498" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M498" s="3" t="n"/>
       <c r="N498" s="2" t="n"/>
     </row>
@@ -27272,11 +27438,15 @@
       <c r="I499" s="3" t="n"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K499" s="2" t="n"/>
-      <c r="L499" s="2" t="n"/>
+      <c r="L499" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M499" s="3" t="n"/>
       <c r="N499" s="2" t="n"/>
     </row>
@@ -27422,7 +27592,7 @@
       </c>
       <c r="J502" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K502" s="2" t="n"/>
@@ -27480,13 +27650,13 @@
       </c>
       <c r="J503" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K503" s="2" t="n"/>
       <c r="L503" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M503" s="3" t="n"/>
@@ -27538,13 +27708,13 @@
       </c>
       <c r="J504" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K504" s="2" t="n"/>
       <c r="L504" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M504" s="3" t="n"/>
@@ -27596,13 +27766,13 @@
       </c>
       <c r="J505" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K505" s="2" t="n"/>
       <c r="L505" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M505" s="3" t="n"/>
@@ -27654,13 +27824,13 @@
       </c>
       <c r="J506" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K506" s="2" t="n"/>
       <c r="L506" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M506" s="3" t="n"/>
@@ -27704,11 +27874,15 @@
       <c r="I507" s="3" t="n"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K507" s="2" t="n"/>
-      <c r="L507" s="2" t="n"/>
+      <c r="L507" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M507" s="3" t="n"/>
       <c r="N507" s="2" t="n"/>
     </row>
@@ -27754,11 +27928,15 @@
       <c r="I508" s="3" t="n"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K508" s="2" t="n"/>
-      <c r="L508" s="2" t="n"/>
+      <c r="L508" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M508" s="3" t="n"/>
       <c r="N508" s="2" t="n"/>
     </row>
@@ -27804,11 +27982,15 @@
       <c r="I509" s="3" t="n"/>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K509" s="2" t="n"/>
-      <c r="L509" s="2" t="n"/>
+      <c r="L509" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M509" s="3" t="n"/>
       <c r="N509" s="2" t="n"/>
     </row>
@@ -27850,11 +28032,15 @@
       <c r="I510" s="3" t="n"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K510" s="2" t="n"/>
-      <c r="L510" s="2" t="n"/>
+      <c r="L510" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M510" s="3" t="n"/>
       <c r="N510" s="2" t="n"/>
     </row>
@@ -27904,7 +28090,11 @@
         </is>
       </c>
       <c r="K511" s="2" t="n"/>
-      <c r="L511" s="2" t="n"/>
+      <c r="L511" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M511" s="3" t="n"/>
       <c r="N511" s="2" t="n"/>
     </row>
@@ -27950,11 +28140,15 @@
       <c r="I512" s="3" t="n"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K512" s="2" t="n"/>
-      <c r="L512" s="2" t="n"/>
+      <c r="L512" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M512" s="3" t="n"/>
       <c r="N512" s="2" t="n"/>
     </row>
@@ -28000,11 +28194,15 @@
       <c r="I513" s="3" t="n"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K513" s="2" t="n"/>
-      <c r="L513" s="2" t="n"/>
+      <c r="L513" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M513" s="3" t="n"/>
       <c r="N513" s="2" t="n"/>
     </row>
@@ -28046,11 +28244,15 @@
       <c r="I514" s="3" t="n"/>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K514" s="2" t="n"/>
-      <c r="L514" s="2" t="n"/>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M514" s="3" t="n"/>
       <c r="N514" s="2" t="n"/>
     </row>
@@ -28096,11 +28298,15 @@
       <c r="I515" s="3" t="n"/>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K515" s="2" t="n"/>
-      <c r="L515" s="2" t="n"/>
+      <c r="L515" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M515" s="3" t="n"/>
       <c r="N515" s="2" t="n"/>
     </row>
@@ -28146,11 +28352,15 @@
       <c r="I516" s="3" t="n"/>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K516" s="2" t="n"/>
-      <c r="L516" s="2" t="n"/>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M516" s="3" t="n"/>
       <c r="N516" s="2" t="n"/>
     </row>
@@ -28196,11 +28406,15 @@
       <c r="I517" s="3" t="n"/>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K517" s="2" t="n"/>
-      <c r="L517" s="2" t="n"/>
+      <c r="L517" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M517" s="3" t="n"/>
       <c r="N517" s="2" t="n"/>
     </row>
@@ -28242,11 +28456,15 @@
       <c r="I518" s="3" t="n"/>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K518" s="2" t="n"/>
-      <c r="L518" s="2" t="n"/>
+      <c r="L518" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M518" s="3" t="n"/>
       <c r="N518" s="2" t="n"/>
     </row>
@@ -28292,11 +28510,15 @@
       <c r="I519" s="3" t="n"/>
       <c r="J519" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K519" s="2" t="n"/>
-      <c r="L519" s="2" t="n"/>
+      <c r="L519" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M519" s="3" t="n"/>
       <c r="N519" s="2" t="n"/>
     </row>
@@ -28438,11 +28660,15 @@
       <c r="I522" s="3" t="n"/>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K522" s="2" t="n"/>
-      <c r="L522" s="2" t="n"/>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M522" s="3" t="n"/>
       <c r="N522" s="2" t="n"/>
     </row>
@@ -32220,11 +32446,15 @@
       <c r="I586" s="15" t="n"/>
       <c r="J586" s="15" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K586" s="15" t="n"/>
-      <c r="L586" s="15" t="n"/>
+      <c r="L586" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M586" s="15" t="n"/>
     </row>
     <row r="587">
@@ -32269,11 +32499,15 @@
       <c r="I587" s="15" t="n"/>
       <c r="J587" s="15" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K587" s="15" t="n"/>
-      <c r="L587" s="15" t="n"/>
+      <c r="L587" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M587" s="15" t="n"/>
     </row>
     <row r="588">
@@ -32318,11 +32552,15 @@
       <c r="I588" s="15" t="n"/>
       <c r="J588" s="15" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K588" s="15" t="n"/>
-      <c r="L588" s="15" t="n"/>
+      <c r="L588" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M588" s="15" t="n"/>
     </row>
     <row r="589">
@@ -33836,7 +34074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35076,6 +35314,156 @@
       <c r="F43" t="inlineStr">
         <is>
           <t>提示语配色规范</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CK-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>查询 / 检查信息</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>检查页·设备类型分行</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>有屏蔽设备时「其他」类型显示一个超大数字。形态是典型的无符号下溢——「其他」多半按『总数 − 各已知类型之和』算，屏蔽点被从某个分项里扣掉却没从总数扣，差值变负后按 unsigned 打印。与 CK-08 同属检查页的屏蔽计数链路</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ 检查页屏蔽计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CK-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>查询 / 检查信息</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>检查页·屏蔽数量列</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>有屏蔽设备时每一行的屏蔽数据全是 0（原记录为该列空白）。屏蔽数没有汇进分类型行，与 CK-04 的超大数字互为表里：一边少算一边多算，指向同一处计数</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>★ 检查页屏蔽计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OP-01.2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>设置 / 操作模式设置</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ⅰ 级拒绝项·手自动切换未受保护</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>❌ 一级操作员（无需密码）可以操作手自动切换。⚠️ 这不只是操作级别越权：5.4.2.2 给手/自动转换规定的是自复位钥匙开关，即一道物理准入；软件侧放开到 Ⅰ 级等于绕过它。后果是任何能靠近机柜的人都能把系统切到手动、使自动联动失效而面板无异常。建议按 P0 重估，并同步复核 UI-17.2 操作模式页的准入等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UI-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 节点设备监控</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>节点设备监控·查询无响应</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>节点监控页查询无响应（本页另有 UI-07.4 返回按钮缺陷，属全局导航缺陷）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GE-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>气灭 / 启动流程</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>②⑤ 喷洒声警报缺失</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>❌ 启动倒计时开始时声光报警器无声，倒计时结束后仍无声，应有喷洒声。⚠️ 台账自相矛盾：本总案判不通过，但子项 GE-02.4「② 声光警报器」与 GE-02.10「⑤ 喷洒声光」都判了通过——两者须复测，很可能当初只验了光没验声。与 GE-22（强启后放气勿入指示牌未亮）合看，形态是『光通声不通 / 现场警示件驱动缺失』，指向喷洒警报输出链路而非单个器件</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>GE-22 放气勿入指示牌未亮</t>
         </is>
       </c>
     </row>
